--- a/Result/profitability/8422.xlsx
+++ b/Result/profitability/8422.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>3.52</v>
       </c>
       <c r="M2" t="n">
-        <v>2.5525</v>
+        <v>2.27</v>
       </c>
       <c r="N2" t="n">
-        <v>48.33</v>
+        <v>46.56875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>10.76</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5725</v>
+        <v>3.195</v>
       </c>
       <c r="N3" t="n">
-        <v>49.0925</v>
+        <v>47.54625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,16 +899,16 @@
         <v>1.95</v>
       </c>
       <c r="M4" t="n">
-        <v>3.39625</v>
+        <v>2.9425</v>
       </c>
       <c r="N4" t="n">
-        <v>48.90625</v>
+        <v>46.24250000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,16 +1018,16 @@
         <v>2.31</v>
       </c>
       <c r="M5" t="n">
-        <v>3.18875</v>
+        <v>2.7275</v>
       </c>
       <c r="N5" t="n">
-        <v>47.63375000000001</v>
+        <v>44.15</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>2.84</v>
       </c>
       <c r="M6" t="n">
-        <v>3.04</v>
+        <v>2.7725</v>
       </c>
       <c r="N6" t="n">
-        <v>46.515</v>
+        <v>44.39</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>2.88</v>
       </c>
       <c r="M7" t="n">
-        <v>3.09</v>
+        <v>3.10125</v>
       </c>
       <c r="N7" t="n">
-        <v>47.71625</v>
+        <v>45.47875000000001</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -9064,6 +9064,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>8422</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2268</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1548</v>
+      </c>
+      <c r="E69" t="n">
+        <v>720</v>
+      </c>
+      <c r="F69" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="G69" t="n">
+        <v>553</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>24.37%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J69" t="n">
+        <v>547</v>
+      </c>
+      <c r="K69" t="n">
+        <v>459</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2.155</v>
+      </c>
+      <c r="N69" t="n">
+        <v>47.61624999999999</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="X69" t="n">
+        <v>0.6190476190476193</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>-16.47</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>-0.3416303671437462</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>-3.69</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-0.9156327543424317</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-27.87</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-0.4675390035228989</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
